--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>102257</v>
+        <v>102267</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>102267</v>
+        <v>102280</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>102280</v>
+        <v>102285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>102285</v>
+        <v>102294</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>1403</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Skånebjörnbär</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>102294</v>
+        <v>102307</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>1403</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Skånebjörnbär</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>102307</v>
+        <v>102320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>102320</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103070</v>
+        <v>103071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103071</v>
+        <v>103074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103074</v>
+        <v>103079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103079</v>
+        <v>103085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103085</v>
+        <v>103086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103086</v>
+        <v>103087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103087</v>
+        <v>103088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103088</v>
+        <v>103089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103089</v>
+        <v>103095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103095</v>
+        <v>103099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45832-2023 artfynd.xlsx
+++ b/artfynd/A 45832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122208648</v>
       </c>
       <c r="B2" t="n">
-        <v>103099</v>
+        <v>103104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
